--- a/output/pdf_financials_xlsx/INX.xlsx
+++ b/output/pdf_financials_xlsx/INX.xlsx
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.7162269999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.785745</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.368701</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.409272</v>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.7162269999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.785745</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.368701</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.409272</v>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.844397</v>
+        <v>0.12817</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.900898</v>
+        <v>0.115153</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.466518</v>
+        <v>0.097817</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.263282</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">

--- a/output/pdf_financials_xlsx/INX.xlsx
+++ b/output/pdf_financials_xlsx/INX.xlsx
@@ -2977,22 +2977,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.207961</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.255978</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.329577</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.486684</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.499253</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.404744</v>
       </c>
     </row>
     <row r="101">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.008388</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.00043</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.004744</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.003552</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.008905</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.026058</v>
       </c>
     </row>
     <row r="113">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7372,7 +7372,11 @@
           <t>Proceeds on disposal of property and equipment $</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -7808,7 +7812,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8434,7 +8438,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>0.008388</v>
       </c>
@@ -8648,7 +8656,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9594,7 +9602,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9776,7 +9784,11 @@
           <t>Loss on disposal of property and equipment 15</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -10500,7 +10512,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -10822,7 +10834,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>0.030365</v>
       </c>

--- a/output/pdf_financials_xlsx/INX.xlsx
+++ b/output/pdf_financials_xlsx/INX.xlsx
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.133984</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.06975199999999999</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -3127,22 +3127,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.375895</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.179351</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.726959</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>0.240125</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.27973</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.866698</v>
       </c>
     </row>
     <row r="107">
@@ -6922,7 +6922,11 @@
           <t>Net change in non-cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -8040,7 +8044,11 @@
           <t>Deferred tax recovery 24</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8174,7 +8182,11 @@
           <t>Net change in non-cash operating working capital 22</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -8926,7 +8938,11 @@
           <t>Deferred tax recovery 23</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -9060,7 +9076,11 @@
           <t>Net change in non-cash operating working capital 21</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9832,7 +9852,11 @@
           <t>Deferred tax recovery 25</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -10060,7 +10084,11 @@
           <t>Net change in non-cash operating working capital 23</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -10882,7 +10910,11 @@
           <t>Deferred tax recovery 27</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.093649</v>
       </c>
@@ -11060,7 +11092,11 @@
           <t>Net change in non-cash operating working capital 25</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>0.375895</v>
       </c>
@@ -12660,7 +12696,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -13740,7 +13780,11 @@
           <t>Loss from discontinued operations 11</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -14544,7 +14588,11 @@
           <t>Loss from discontinued operations 13</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E236" s="5" t="n">
         <v>-0.133984</v>
       </c>
